--- a/file/table/DAPC_QuizM01A02a2Espiral.xlsx
+++ b/file/table/DAPC_QuizM01A02a2Espiral.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29123"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29727"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB80C55-58CD-4C3A-BCA8-A990A9A6FF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E876E35-9F7B-497B-85B5-C799D80777C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{4FA0F644-0B27-48D7-AC0A-327E78D1DF86}"/>
   </bookViews>
   <sheets>
-    <sheet name="Espiral" sheetId="1" r:id="rId1"/>
+    <sheet name="Espiral2CentrosSDig" sheetId="2" r:id="rId1"/>
+    <sheet name="Espiral2CentrosFactor" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,8 +36,31 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Test</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{5DBA6237-70AB-4AB6-88B8-9285E275DD2A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Último dígito de su código de alumno en Enlace Académico.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="11">
   <si>
     <t>Arco</t>
   </si>
@@ -44,7 +68,16 @@
     <t>Código</t>
   </si>
   <si>
-    <t>R</t>
+    <t>r</t>
+  </si>
+  <si>
+    <t>Radio r en metros</t>
+  </si>
+  <si>
+    <t>Long (m)</t>
+  </si>
+  <si>
+    <t>Factor:</t>
   </si>
   <si>
     <r>
@@ -58,27 +91,39 @@
         <rFont val="Segoe UI Light"/>
         <family val="2"/>
       </rPr>
-      <t>M01A02a-2 / Espiral</t>
+      <t>M01A02a-2 / Espiral de dos centros usando factor</t>
     </r>
   </si>
   <si>
-    <t>r</t>
+    <t>Factor</t>
   </si>
   <si>
-    <t>Radio r en metros</t>
+    <t>SDig</t>
   </si>
   <si>
-    <t>Long (m)</t>
+    <r>
+      <t xml:space="preserve">Quiz </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>M01A02a-2 / Espiral de dos centros usando factor y SDig</t>
+    </r>
   </si>
   <si>
-    <t>Factor:</t>
+    <t>radio</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,6 +148,12 @@
       <sz val="11"/>
       <color rgb="FF0070C0"/>
       <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -327,6 +378,55 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>348155</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>111672</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>551489</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>148812</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9478C50A-E9AA-48DC-8904-8D979E3D4F25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1806465" y="742293"/>
+          <a:ext cx="3438550" cy="3400450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -691,7 +791,131 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EBE33F6-12AF-4DD9-A5AD-2A0BD4ECCEC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39BE74C5-5229-45D6-9D44-FAB954EBC922}">
+  <dimension ref="B2:C15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.06640625" style="1"/>
+    <col min="3" max="3" width="6.1328125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.59765625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.06640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
+      <c r="C7" s="12">
+        <f>C4</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B8" s="8">
+        <v>2</v>
+      </c>
+      <c r="C8" s="12">
+        <f>ROUND(C7+(C$4/10)^(1/B8)+$C$3^(1/B8),2)</f>
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B9" s="8">
+        <v>3</v>
+      </c>
+      <c r="C9" s="12">
+        <f>ROUND(C8+(C$4/10)^(1/B9)+$C$3^(1/B9),2)</f>
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B10" s="8">
+        <v>4</v>
+      </c>
+      <c r="C10" s="12">
+        <f>ROUND(C9+(C$4/10)^(1/B10)+$C$3^(1/B10),2)</f>
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B11" s="8">
+        <v>5</v>
+      </c>
+      <c r="C11" s="12">
+        <f>ROUND(C10+(C$4/10)^(1/B11)+$C$3^(1/B11),2)</f>
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B12" s="8">
+        <v>6</v>
+      </c>
+      <c r="C12" s="12">
+        <f>ROUND(C11+(C$4/10)^(1/B12)+$C$3^(1/B12),2)</f>
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B13" s="8">
+        <v>7</v>
+      </c>
+      <c r="C13" s="12">
+        <f>ROUND(C12+(C$4/10)^(1/B13)+$C$3^(1/B13),2)</f>
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B14" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="14">
+        <f>(SUM(C7:C13)/2)*2*PI()</f>
+        <v>107.6623802385222</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B15" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EBE33F6-12AF-4DD9-A5AD-2A0BD4ECCEC5}">
   <dimension ref="B2:L15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
@@ -704,15 +928,15 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.6">
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.6">
@@ -755,34 +979,34 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.6">
@@ -826,43 +1050,43 @@
       </c>
       <c r="C8" s="11">
         <f>ROUND(C7+(C$5/10)^(1/B8)+$C$3^(1/B8),2)</f>
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="D8" s="11">
         <f t="shared" ref="D8:L13" si="0">ROUND(D7+(D$5/10)^(1/C8)+$C$3^(1/C8),2)</f>
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="E8" s="11">
         <f t="shared" si="0"/>
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="0"/>
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="G8" s="11">
         <f t="shared" si="0"/>
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="H8" s="11">
         <f t="shared" si="0"/>
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="I8" s="11">
         <f t="shared" si="0"/>
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="J8" s="11">
         <f t="shared" si="0"/>
-        <v>2.25</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="K8" s="11">
         <f t="shared" si="0"/>
-        <v>2.3199999999999998</v>
+        <v>2.39</v>
       </c>
       <c r="L8" s="12">
         <f t="shared" si="0"/>
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.6">
@@ -871,43 +1095,43 @@
       </c>
       <c r="C9" s="11">
         <f t="shared" ref="C9:C13" si="1">ROUND(C8+(C$5/10)^(1/B9)+$C$3^(1/B9),2)</f>
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="D9" s="11">
         <f t="shared" si="0"/>
-        <v>2.0699999999999998</v>
+        <v>2.23</v>
       </c>
       <c r="E9" s="11">
         <f t="shared" si="0"/>
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" si="0"/>
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="G9" s="11">
         <f t="shared" si="0"/>
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="H9" s="11">
         <f t="shared" si="0"/>
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="I9" s="11">
         <f t="shared" si="0"/>
-        <v>3.59</v>
+        <v>3.71</v>
       </c>
       <c r="J9" s="11">
         <f t="shared" si="0"/>
-        <v>3.73</v>
+        <v>3.86</v>
       </c>
       <c r="K9" s="11">
         <f t="shared" si="0"/>
-        <v>3.85</v>
+        <v>3.98</v>
       </c>
       <c r="L9" s="12">
         <f t="shared" si="0"/>
-        <v>3.95</v>
+        <v>4.0599999999999996</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.6">
@@ -916,43 +1140,43 @@
       </c>
       <c r="C10" s="11">
         <f t="shared" si="1"/>
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="D10" s="11">
         <f t="shared" si="0"/>
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="E10" s="11">
         <f t="shared" si="0"/>
-        <v>3.51</v>
+        <v>3.79</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" si="0"/>
-        <v>4.08</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="G10" s="11">
         <f t="shared" si="0"/>
-        <v>4.5599999999999996</v>
+        <v>4.78</v>
       </c>
       <c r="H10" s="11">
         <f t="shared" si="0"/>
-        <v>4.91</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I10" s="11">
         <f t="shared" si="0"/>
-        <v>5.16</v>
+        <v>5.33</v>
       </c>
       <c r="J10" s="11">
         <f t="shared" si="0"/>
-        <v>5.35</v>
+        <v>5.52</v>
       </c>
       <c r="K10" s="11">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="L10" s="12">
         <f t="shared" si="0"/>
-        <v>5.63</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.6">
@@ -961,43 +1185,43 @@
       </c>
       <c r="C11" s="11">
         <f t="shared" si="1"/>
-        <v>3.17</v>
+        <v>3.34</v>
       </c>
       <c r="D11" s="11">
         <f t="shared" si="0"/>
-        <v>3.94</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="E11" s="11">
         <f t="shared" si="0"/>
-        <v>4.78</v>
+        <v>5.15</v>
       </c>
       <c r="F11" s="11">
         <f t="shared" si="0"/>
-        <v>5.52</v>
+        <v>5.86</v>
       </c>
       <c r="G11" s="11">
         <f t="shared" si="0"/>
-        <v>6.11</v>
+        <v>6.38</v>
       </c>
       <c r="H11" s="11">
         <f t="shared" si="0"/>
-        <v>6.53</v>
+        <v>6.76</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="0"/>
-        <v>6.82</v>
+        <v>7.03</v>
       </c>
       <c r="J11" s="11">
         <f t="shared" si="0"/>
-        <v>7.05</v>
+        <v>7.25</v>
       </c>
       <c r="K11" s="11">
         <f t="shared" si="0"/>
-        <v>7.23</v>
+        <v>7.43</v>
       </c>
       <c r="L11" s="12">
         <f t="shared" si="0"/>
-        <v>7.38</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.6">
@@ -1006,43 +1230,43 @@
       </c>
       <c r="C12" s="11">
         <f t="shared" si="1"/>
-        <v>3.89</v>
+        <v>4.09</v>
       </c>
       <c r="D12" s="11">
         <f t="shared" si="0"/>
-        <v>5.0999999999999996</v>
+        <v>5.5</v>
       </c>
       <c r="E12" s="11">
         <f t="shared" si="0"/>
-        <v>6.19</v>
+        <v>6.63</v>
       </c>
       <c r="F12" s="11">
         <f t="shared" si="0"/>
-        <v>7.07</v>
+        <v>7.47</v>
       </c>
       <c r="G12" s="11">
         <f t="shared" si="0"/>
-        <v>7.75</v>
+        <v>8.06</v>
       </c>
       <c r="H12" s="11">
         <f t="shared" si="0"/>
-        <v>8.2200000000000006</v>
+        <v>8.49</v>
       </c>
       <c r="I12" s="11">
         <f t="shared" si="0"/>
-        <v>8.5500000000000007</v>
+        <v>8.7899999999999991</v>
       </c>
       <c r="J12" s="11">
         <f t="shared" si="0"/>
-        <v>8.8000000000000007</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="K12" s="11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>9.23</v>
       </c>
       <c r="L12" s="12">
         <f t="shared" si="0"/>
-        <v>9.17</v>
+        <v>9.3800000000000008</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.6">
@@ -1051,97 +1275,98 @@
       </c>
       <c r="C13" s="11">
         <f t="shared" si="1"/>
-        <v>4.6500000000000004</v>
+        <v>4.87</v>
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
-        <v>6.36</v>
+        <v>6.83</v>
       </c>
       <c r="E13" s="11">
         <f t="shared" si="0"/>
-        <v>7.7</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" si="0"/>
-        <v>8.6999999999999993</v>
+        <v>9.14</v>
       </c>
       <c r="G13" s="11">
         <f t="shared" si="0"/>
-        <v>9.4499999999999993</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="0"/>
-        <v>9.9600000000000009</v>
+        <v>10.26</v>
       </c>
       <c r="I13" s="11">
         <f t="shared" si="0"/>
-        <v>10.32</v>
+        <v>10.59</v>
       </c>
       <c r="J13" s="11">
         <f t="shared" si="0"/>
-        <v>10.59</v>
+        <v>10.85</v>
       </c>
       <c r="K13" s="11">
         <f t="shared" si="0"/>
-        <v>10.81</v>
+        <v>11.06</v>
       </c>
       <c r="L13" s="12">
         <f t="shared" si="0"/>
-        <v>10.99</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.6">
       <c r="B14" s="10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" s="13">
         <f>(SUM(C7:C13)/2)*2*PI()</f>
-        <v>58.025216311803476</v>
+        <v>60.726985993890708</v>
       </c>
       <c r="D14" s="13">
         <f t="shared" ref="D14:L14" si="2">(SUM(D7:D13)/2)*2*PI()</f>
-        <v>71.659728428383175</v>
+        <v>76.969020012949926</v>
       </c>
       <c r="E14" s="13">
         <f t="shared" si="2"/>
-        <v>85.357072398034688</v>
+        <v>91.231850660247588</v>
       </c>
       <c r="F14" s="13">
         <f t="shared" si="2"/>
-        <v>97.138044848996401</v>
+        <v>102.57300013970674</v>
       </c>
       <c r="G14" s="13">
         <f t="shared" si="2"/>
-        <v>106.59423873630168</v>
+        <v>110.9296365982556</v>
       </c>
       <c r="H14" s="13">
         <f t="shared" si="2"/>
-        <v>113.34866294151975</v>
+        <v>117.11857412582749</v>
       </c>
       <c r="I14" s="13">
         <f t="shared" si="2"/>
-        <v>118.15529970151212</v>
+        <v>121.5168038408532</v>
       </c>
       <c r="J14" s="13">
         <f t="shared" si="2"/>
-        <v>121.79954717967627</v>
+        <v>125.12963539248146</v>
       </c>
       <c r="K14" s="13">
         <f t="shared" si="2"/>
-        <v>124.75264427405068</v>
+        <v>128.05131656031998</v>
       </c>
       <c r="L14" s="14">
         <f t="shared" si="2"/>
-        <v>127.23450247038662</v>
+        <v>130.21901549129694</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.6">
       <c r="B15" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>